--- a/Statistics/400m Medley_statistics.xlsx
+++ b/Statistics/400m Medley_statistics.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,25 +1132,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Kristian Volden</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5.10,41</t>
+          <t>5.10,02</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26.10.2013</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1167,20 +1167,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jenny Marandon Natvik</t>
+          <t>Olav Nygård Bergum</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5.42,42</t>
+          <t>5.09,92</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>17.01.2016</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1202,25 +1202,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sondre Brunvoll Møllerløkken</t>
+          <t>Jenny Marandon Natvik</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5.10,88</t>
+          <t>5.42,42</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>17.01.2016</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1237,25 +1237,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kristoffer Loeng</t>
+          <t>Kristian Volden</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5.11,20</t>
+          <t>5.10,41</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>31.10.2015</t>
+          <t>26.10.2013</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1272,25 +1272,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Simon Moe</t>
+          <t>Sondre Brunvoll Møllerløkken</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5.12,68</t>
+          <t>5.10,88</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>10.05.2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1307,20 +1307,20 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Margaret Kjøraas</t>
+          <t>Kristoffer Loeng</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5.48,26</t>
+          <t>5.11,20</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>31.10.2015</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1342,25 +1342,25 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Morten Olden Larsen</t>
+          <t>Simon Moe</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5.16,92</t>
+          <t>5.12,68</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>23.10.2016</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1377,20 +1377,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Vårin Berge Jensås</t>
+          <t>Margaret Kjøraas</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5.54,89</t>
+          <t>5.48,26</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22.06.2019</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1412,20 +1412,20 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Joakim Gjerde</t>
+          <t>Morten Olden Larsen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5.29,26</t>
+          <t>5.16,92</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>362</v>
+        <v>406</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>25.10.2014</t>
+          <t>23.10.2016</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1447,25 +1447,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Daniel Moen Manriquez</t>
+          <t>Vårin Berge Jensås</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5.32,05</t>
+          <t>5.54,89</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>353</v>
+        <v>388</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>09.10.2016</t>
+          <t>22.06.2019</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1482,20 +1482,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Thomas Trøite</t>
+          <t>Emmelin Munkhaugen</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5.32,70</t>
+          <t>5.52,64</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>13.11.2021</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1517,25 +1517,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Einar Woldseth</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5.40,15</t>
+          <t>5.28,65</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>328</v>
+        <v>364</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1552,20 +1552,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jakob Isaksen</t>
+          <t>Joakim Gjerde</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5.43,36</t>
+          <t>5.29,26</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>319</v>
+        <v>362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>23.10.2022</t>
+          <t>25.10.2014</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1587,25 +1587,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Erlend Søderlund</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5.48,90</t>
+          <t>5.29,57</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>304</v>
+        <v>361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>11.03.2011</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1622,20 +1622,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Storm Olander Øvergård</t>
+          <t>Mattias Isaksen</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5.51,43</t>
+          <t>5.31,33</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>298</v>
+        <v>355</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1657,25 +1657,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Philip Giske Nyman</t>
+          <t>Daniel Moen Manriquez</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6.03,03</t>
+          <t>5.32,05</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>270</v>
+        <v>353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>09.10.2016</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1692,25 +1692,25 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sondre Grimsmo</t>
+          <t>Thomas Trøite</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6.05,25</t>
+          <t>5.32,70</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>265</v>
+        <v>351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>12.05.2007</t>
+          <t>13.11.2021</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1727,25 +1727,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alfred Fenstad Høysæter</t>
+          <t>Einar Woldseth</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6.07,37</t>
+          <t>5.40,15</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>16.11.2019</t>
+          <t>15.02.2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kolvereid</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1762,20 +1762,20 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bjørn Erik Ystenes</t>
+          <t>Storm Olander Øvergård</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6.08,06</t>
+          <t>5.41,57</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>259</v>
+        <v>324</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>18.09.2011</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1797,25 +1797,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Vegard Skjervold</t>
+          <t>Ludvig Svendsen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6.12,66</t>
+          <t>5.42,21</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>250</v>
+        <v>323</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22.10.2017</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1832,25 +1832,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Theodor Solheim</t>
+          <t>Jakob Isaksen</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6.24,01</t>
+          <t>5.43,36</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>228</v>
+        <v>319</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>16.11.2019</t>
+          <t>23.10.2022</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1867,16 +1867,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jon Olav Båtbukt</t>
+          <t>Erlend Søderlund</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6.24,37</t>
+          <t>5.48,90</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>227</v>
+        <v>304</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1902,25 +1902,25 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Vegard Maaø</t>
+          <t>Philip Giske Nyman</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6.27,19</t>
+          <t>6.03,03</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>223</v>
+        <v>270</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>28.02.2009</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stjørdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1937,25 +1937,25 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Brage Gylseth Dahl</t>
+          <t>Eirik Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6.28,09</t>
+          <t>6.03,11</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>221</v>
+        <v>270</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1972,25 +1972,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Morten Schanke</t>
+          <t>Sondre Grimsmo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6.28,71</t>
+          <t>6.05,25</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>220</v>
+        <v>265</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>25.03.2017</t>
+          <t>12.05.2007</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2007,25 +2007,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>David Csejtey</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6.38,08</t>
+          <t>6.06,89</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>205</v>
+        <v>262</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22.06.2019</t>
+          <t>19.10.2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Verdal</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2042,20 +2042,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Henning Andersson</t>
+          <t>Alfred Fenstad Høysæter</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6.40,31</t>
+          <t>6.07,37</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>201</v>
+        <v>261</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>19.09.2010</t>
+          <t>16.11.2019</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2077,25 +2077,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Paal Aagaard</t>
+          <t>Bjørn Erik Ystenes</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6.41,83</t>
+          <t>6.08,06</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>199</v>
+        <v>259</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>13.03.2009</t>
+          <t>18.09.2011</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kirkenes</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2112,25 +2112,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Njål Høie</t>
+          <t>Vegard Skjervold</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6.48,60</t>
+          <t>6.12,66</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>189</v>
+        <v>250</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>15.09.2013</t>
+          <t>22.10.2017</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2147,20 +2147,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Eirik Hamnes Ulriksen</t>
+          <t>Theodor Solheim</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6.49,98</t>
+          <t>6.24,01</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>187</v>
+        <v>228</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>08.06.2024</t>
+          <t>16.11.2019</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2182,25 +2182,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Gunhild Furuholt Valle</t>
+          <t>Jon Olav Båtbukt</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7.35,20</t>
+          <t>6.24,37</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>184</v>
+        <v>227</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>11.03.2011</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2217,25 +2217,25 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Edvin Grenne Spangelo</t>
+          <t>Vegard Maaø</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6.57,72</t>
+          <t>6.27,19</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>177</v>
+        <v>223</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>20.10.2024</t>
+          <t>28.02.2009</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Stjørdal</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2252,33 +2252,313 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Brage Gylseth Dahl</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>6.28,09</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>221</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>15.02.2025</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Kolvereid</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Morten Schanke</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>6.28,71</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>220</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>25.03.2017</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Liv Løfaldli</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7.03,15</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>220</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>08.11.2025</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Gunhild Furuholt Valle</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7.11,08</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>208</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>19.10.2025</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Verdal</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>David Csejtey</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>6.38,08</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>205</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>22.06.2019</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Ingeborg Strandenes</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>7.43,59</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>174</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>21.06.2025</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>7.13,67</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>204</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>19.10.2025</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Verdal</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Henning Andersson</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>6.40,31</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>201</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>19.09.2010</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Paal Aagaard</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>6.41,83</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>199</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>13.03.2009</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Kirkenes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Njål Høie</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>6.48,60</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>189</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>15.09.2013</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3536,7 +3816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4279,20 +4559,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Malin Schanke Tømmervik</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5.49,70</t>
+          <t>5.44,96</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>24.05.2008</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4314,25 +4594,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Viktoria Juel</t>
+          <t>Malin Schanke Tømmervik</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5.50,88</t>
+          <t>5.49,70</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20.03.2010</t>
+          <t>24.05.2008</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4349,25 +4629,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Silje Aadahl</t>
+          <t>Sissel Furuholt Valle</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5.51,31</t>
+          <t>5.46,07</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>01.10.2017</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4384,25 +4664,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nora Yian Baldersheim</t>
+          <t>Viktoria Juel</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5.52,90</t>
+          <t>5.50,88</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>13.11.2021</t>
+          <t>20.03.2010</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4419,25 +4699,25 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Marthe Kalvik</t>
+          <t>Silje Aadahl</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5.55,12</t>
+          <t>5.51,31</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08.10.2006</t>
+          <t>01.10.2017</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4454,20 +4734,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lisa Ling Klauseth Liasjø</t>
+          <t>Nora Yian Baldersheim</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5.55,95</t>
+          <t>5.52,90</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>16.11.2019</t>
+          <t>13.11.2021</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4489,20 +4769,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Hege Solberg Jørgensen</t>
+          <t>Marthe Kalvik</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5.57,97</t>
+          <t>5.55,12</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20.05.2017</t>
+          <t>08.10.2006</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4524,25 +4804,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Elise Nygård</t>
+          <t>Lisa Ling Klauseth Liasjø</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5.58,41</t>
+          <t>5.55,95</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11.03.2011</t>
+          <t>16.11.2019</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4559,25 +4839,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Elisabeth Wilmann</t>
+          <t>Hege Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6.00,40</t>
+          <t>5.57,97</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>01.10.2017</t>
+          <t>20.05.2017</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4594,16 +4874,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Kristina Elena Bjørklund Mora</t>
+          <t>Elise Nygård</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6.01,05</t>
+          <t>5.58,41</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4629,25 +4909,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Carina Aadahl</t>
+          <t>Elisabeth Wilmann</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6.02,31</t>
+          <t>6.00,40</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>19.01.2014</t>
+          <t>01.10.2017</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4664,25 +4944,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nina Alicja Skarø</t>
+          <t>Kristina Elena Bjørklund Mora</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6.03,22</t>
+          <t>6.01,05</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20.05.2017</t>
+          <t>11.03.2011</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4699,25 +4979,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Eirill Straum</t>
+          <t>Carina Aadahl</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6.07,51</t>
+          <t>6.02,31</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>23.10.2016</t>
+          <t>19.01.2014</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4734,20 +5014,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Kine Marie Sørensen</t>
+          <t>Nina Alicja Skarø</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6.08,20</t>
+          <t>6.03,22</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20.05.2006</t>
+          <t>20.05.2017</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4769,25 +5049,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Mila Maria Flåan</t>
+          <t>Marie Skuseth</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6.09,05</t>
+          <t>6.02,55</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>23.10.2022</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4804,20 +5084,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Thea Lervold Høffler</t>
+          <t>Eirill Straum</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6.12,19</t>
+          <t>6.07,51</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>26.10.2013</t>
+          <t>23.10.2016</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4839,20 +5119,20 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Frida Pauline Busch</t>
+          <t>Kine Marie Sørensen</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6.20,35</t>
+          <t>6.08,20</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>315</v>
+        <v>347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>13.11.2021</t>
+          <t>20.05.2006</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4874,25 +5154,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Embla Mimi Baarholm</t>
+          <t>Mila Maria Flåan</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6.24,70</t>
+          <t>6.09,05</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20.05.2017</t>
+          <t>23.10.2022</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4909,25 +5189,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Thora Bjarnøe Brandsegg</t>
+          <t>Thea Lervold Høffler</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6.26,32</t>
+          <t>6.12,19</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>301</v>
+        <v>336</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>26.10.2013</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4944,20 +5224,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Hedda Østgaard</t>
+          <t>Frida Pauline Busch</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6.30,23</t>
+          <t>6.20,35</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>21.06.2008</t>
+          <t>13.11.2021</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4979,20 +5259,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Emma Lu Tjeldvoll</t>
+          <t>Embla Mimi Baarholm</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6.45,64</t>
+          <t>6.24,70</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>13.11.2021</t>
+          <t>20.05.2017</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5014,20 +5294,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Hedda Grimstad-Johannessen</t>
+          <t>Thora Bjarnøe Brandsegg</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6.46,17</t>
+          <t>6.26,32</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>22.06.2019</t>
+          <t>20.06.2021</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5049,20 +5329,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Emilie Ying Ulstad Hovland</t>
+          <t>Nicole Kulagina</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6.49,67</t>
+          <t>6.23,44</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5084,25 +5364,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Silje Dahle</t>
+          <t>Hedda Østgaard</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6.50,04</t>
+          <t>6.30,23</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>251</v>
+        <v>292</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>22.10.2017</t>
+          <t>21.06.2008</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5119,25 +5399,25 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Nicole Kulagina</t>
+          <t>Emma Lu Tjeldvoll</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6.59,43</t>
+          <t>6.45,64</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>13.11.2021</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5154,20 +5434,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Hedda Grimstad-Johannessen</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7.08,22</t>
+          <t>6.46,17</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>221</v>
+        <v>259</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15.09.2013</t>
+          <t>22.06.2019</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5189,25 +5469,25 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Chloe Branlat</t>
+          <t>Emilie Ying Ulstad Hovland</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7.13,68</t>
+          <t>6.49,67</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>212</v>
+        <v>252</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>28.03.2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5224,33 +5504,138 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Silje Dahle</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>6.50,04</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>251</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>22.10.2017</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Othelie Annette Høie</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7.08,22</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>221</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>15.09.2013</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Chloe Branlat</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>7.13,68</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>212</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>15.02.2025</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Kolvereid</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Ida Fiskaa Barstad</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>7.47,57</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C52" t="n">
         <v>169</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>22.06.2019</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -5415,12 +5800,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Elise Lund</t>
+          <t>Mia Olden Larsen</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.30,43</t>
+          <t>5.30,45</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5428,12 +5813,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>30.06.2019</t>
+          <t>04.03.2016</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5450,12 +5835,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mia Olden Larsen</t>
+          <t>Elise Lund</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.30,45</t>
+          <t>5.30,43</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5463,12 +5848,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>04.03.2016</t>
+          <t>30.06.2019</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">

--- a/Statistics/400m Medley_statistics.xlsx
+++ b/Statistics/400m Medley_statistics.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1132,12 +1132,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Balder Baarholm</t>
+          <t>Sondre Brunvoll Møllerløkken</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5.10,02</t>
+          <t>5.10,01</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>08.11.2025</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1202,20 +1202,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Jenny Marandon Natvik</t>
+          <t>Balder Baarholm</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5.42,42</t>
+          <t>5.10,02</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>17.01.2016</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1237,12 +1237,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Kristian Volden</t>
+          <t>Jenny Marandon Natvik</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5.10,41</t>
+          <t>5.42,42</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26.10.2013</t>
+          <t>17.01.2016</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1272,25 +1272,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sondre Brunvoll Møllerløkken</t>
+          <t>Kristian Volden</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5.10,88</t>
+          <t>5.10,41</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10.05.2025</t>
+          <t>26.10.2013</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1342,20 +1342,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Simon Moe</t>
+          <t>Einar Woldseth</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5.12,68</t>
+          <t>5.11,52</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>16.01.2016</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1377,20 +1377,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Margaret Kjøraas</t>
+          <t>Simon Moe</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5.48,26</t>
+          <t>5.12,68</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>16.01.2016</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1412,25 +1412,25 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Morten Olden Larsen</t>
+          <t>Margaret Kjøraas</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5.16,92</t>
+          <t>5.48,26</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>23.10.2016</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1447,25 +1447,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Vårin Berge Jensås</t>
+          <t>Morten Olden Larsen</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5.54,89</t>
+          <t>5.16,92</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>388</v>
+        <v>406</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22.06.2019</t>
+          <t>23.10.2016</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1482,20 +1482,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Emmelin Munkhaugen</t>
+          <t>Bjørn Eimar Endal Sorteberg</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5.52,64</t>
+          <t>5.21,43</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>08.11.2025</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1517,20 +1517,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lucas Nachappa Muthanna</t>
+          <t>Vårin Berge Jensås</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5.28,65</t>
+          <t>5.54,89</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>08.11.2025</t>
+          <t>22.06.2019</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1552,25 +1552,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Joakim Gjerde</t>
+          <t>Lucas Nachappa Muthanna</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5.29,26</t>
+          <t>5.28,65</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25.10.2014</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1587,25 +1587,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bjørn Eimar Endal Sorteberg</t>
+          <t>Joakim Gjerde</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5.29,57</t>
+          <t>5.29,26</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>08.11.2025</t>
+          <t>25.10.2014</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1727,25 +1727,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Einar Woldseth</t>
+          <t>Storm Olander Øvergård</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5.40,15</t>
+          <t>5.41,57</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1762,16 +1762,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Storm Olander Øvergård</t>
+          <t>Ludvig Svendsen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5.41,57</t>
+          <t>5.42,21</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1797,25 +1797,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ludvig Svendsen</t>
+          <t>Jakob Isaksen</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5.42,21</t>
+          <t>5.43,36</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>08.11.2025</t>
+          <t>23.10.2022</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1832,25 +1832,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Jakob Isaksen</t>
+          <t>Erlend Søderlund</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5.43,36</t>
+          <t>5.48,90</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>23.10.2022</t>
+          <t>11.03.2011</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1867,25 +1867,25 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Erlend Søderlund</t>
+          <t>Edvin Grenne Spangelo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5.48,90</t>
+          <t>5.55,56</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11.03.2011</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1902,20 +1902,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Philip Giske Nyman</t>
+          <t>Eirik Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6.03,03</t>
+          <t>5.55,63</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>21.06.2025</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1937,12 +1937,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Eirik Hamnes Ulriksen</t>
+          <t>Philip Giske Nyman</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6.03,11</t>
+          <t>6.03,03</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>19.10.2025</t>
+          <t>21.06.2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1972,25 +1972,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sondre Grimsmo</t>
+          <t>Ingeborg Strandenes</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6.05,25</t>
+          <t>6.41,38</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>12.05.2007</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2007,20 +2007,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Edvin Grenne Spangelo</t>
+          <t>Sondre Grimsmo</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6.06,89</t>
+          <t>6.05,25</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>19.10.2025</t>
+          <t>12.05.2007</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2357,25 +2357,25 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gunhild Furuholt Valle</t>
+          <t>Cornelius Wik</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7.11,08</t>
+          <t>6.30,98</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>19.10.2025</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Verdal</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2392,20 +2392,20 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>David Csejtey</t>
+          <t>Lilly Fludal Osland</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6.38,08</t>
+          <t>7.13,74</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>22.06.2019</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2427,16 +2427,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ingeborg Strandenes</t>
+          <t>Gunhild Furuholt Valle</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7.13,67</t>
+          <t>7.11,08</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2462,20 +2462,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Henning Andersson</t>
+          <t>David Csejtey</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>6.40,31</t>
+          <t>6.38,08</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>19.09.2010</t>
+          <t>22.06.2019</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2497,25 +2497,25 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Paal Aagaard</t>
+          <t>Henning Andersson</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6.41,83</t>
+          <t>6.40,31</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>13.03.2009</t>
+          <t>19.09.2010</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kirkenes</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2532,33 +2532,138 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>Paal Aagaard</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>6.41,83</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>199</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>13.03.2009</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Kirkenes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>Njål Høie</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>6.48,60</t>
         </is>
       </c>
-      <c r="C61" t="n">
+      <c r="C62" t="n">
         <v>189</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>15.09.2013</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Jesper Julius Sundseth Skjærli</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>7.02,93</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>171</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>25.01.2026</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Sigurd Kristoffersen Torvik</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>7.04,74</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>168</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2575,7 +2680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3598,20 +3703,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sondre Grimsmo</t>
+          <t>Ellen Kristine Eidsmo Hova</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6.09,95</t>
+          <t>6.40,25</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26.04.2008</t>
+          <t>26.04.2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3633,25 +3738,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Mattias Isaksen</t>
+          <t>Eirik Hamnes Ulriksen</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6.16,57</t>
+          <t>6.06,95</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>15.06.2024</t>
+          <t>26.04.2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ankerskogen svømmehall</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3668,25 +3773,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Edvard Hamnes Ulriksen</t>
+          <t>Sondre Grimsmo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6.33,60</t>
+          <t>6.09,95</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>233</v>
+        <v>281</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>14.06.2025</t>
+          <t>26.04.2008</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3703,25 +3808,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Balder Baarholm</t>
+          <t>Mattias Isaksen</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6.48,94</t>
+          <t>6.16,57</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>208</v>
+        <v>267</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>30.04.2022</t>
+          <t>15.06.2024</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Ankerskogen svømmehall</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3738,20 +3843,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Bjørn Erik Ystenes</t>
+          <t>Ingeborg Strandenes</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7.09,82</t>
+          <t>7.06,07</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>179</v>
+        <v>242</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>26.04.2008</t>
+          <t>26.04.2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3773,33 +3878,243 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>Liv Løfaldli</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7.07,33</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>240</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Edvard Hamnes Ulriksen</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>6.33,60</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>233</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>14.06.2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Hamar</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Balder Baarholm</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>6.48,94</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>208</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>30.04.2022</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Hamar</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Bjørn Erik Ystenes</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7.09,82</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>179</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>26.04.2008</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Emil Falkenbo-Skalmerås</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>7.13,21</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>175</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Vishnu Sattanathan</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>7.14,54</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C40" t="n">
         <v>173</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>30.04.2022</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Hamar</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>50m</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Tymofii Dzisiak</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>7.14,45</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>173</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3816,7 +4131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3894,25 +4209,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sara Juul Wolfgang</t>
+          <t>Maria Erikovna Alvestad</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.10,61</t>
+          <t>5.04,16</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>579</v>
+        <v>617</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.03.2016</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3929,25 +4244,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sanna Josefin Husan Ehrnholm</t>
+          <t>Sara Juul Wolfgang</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5.15,46</t>
+          <t>5.10,61</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>553</v>
+        <v>579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18.01.2015</t>
+          <t>13.03.2016</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -3964,20 +4279,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mia Olden Larsen</t>
+          <t>Sanna Josefin Husan Ehrnholm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5.19,28</t>
+          <t>5.15,46</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17.01.2016</t>
+          <t>18.01.2015</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3999,25 +4314,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Irja Gravdahl</t>
+          <t>Mia Olden Larsen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5.22,37</t>
+          <t>5.19,28</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>05.06.2010</t>
+          <t>17.01.2016</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4034,25 +4349,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tove Fludal Haugan</t>
+          <t>Irja Gravdahl</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.25,96</t>
+          <t>5.22,37</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16.04.2005</t>
+          <t>05.06.2010</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ålesund</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -4069,25 +4384,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gudrun Berg Ildstad</t>
+          <t>Tove Fludal Haugan</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5.26,40</t>
+          <t>5.25,96</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23.01.2011</t>
+          <t>16.04.2005</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Ålesund</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4104,20 +4419,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Stine Tveit</t>
+          <t>Gudrun Berg Ildstad</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5.28,00</t>
+          <t>5.26,40</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11.10.2009</t>
+          <t>23.01.2011</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4139,25 +4454,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Christiana Bjørkli</t>
+          <t>Stine Tveit</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5.31,63</t>
+          <t>5.28,00</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>476</v>
+        <v>492</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>29.11.2008</t>
+          <t>11.10.2009</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -4174,25 +4489,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Maja Graczyk</t>
+          <t>Christiana Bjørkli</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5.31,78</t>
+          <t>5.31,63</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>22.06.2019</t>
+          <t>29.11.2008</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4209,25 +4524,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Anne Bostad Hegvold</t>
+          <t>Maja Graczyk</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5.31,89</t>
+          <t>5.31,78</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>01.04.2011</t>
+          <t>22.06.2019</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -4244,25 +4559,25 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Annika Krill</t>
+          <t>Anne Bostad Hegvold</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5.33,50</t>
+          <t>5.31,89</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>04.02.2005</t>
+          <t>01.04.2011</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -4279,25 +4594,25 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Elise Lund</t>
+          <t>Annika Krill</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5.33,68</t>
+          <t>5.33,50</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>04.10.2015</t>
+          <t>04.02.2005</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -4314,25 +4629,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Åse Vigdisdatter Nytrø</t>
+          <t>Elise Lund</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5.34,74</t>
+          <t>5.33,68</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>15.10.2010</t>
+          <t>04.10.2015</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lambertseter</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -4349,25 +4664,25 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Amanda Husan Ehrnholm</t>
+          <t>Åse Vigdisdatter Nytrø</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5.37,31</t>
+          <t>5.34,74</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17.01.2016</t>
+          <t>15.10.2010</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Lambertseter</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4384,20 +4699,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Maria Erikovna Alvestad</t>
+          <t>Amanda Husan Ehrnholm</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5.39,67</t>
+          <t>5.37,31</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>17.01.2016</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4419,20 +4734,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Maud Steinsdotter Nestgaard</t>
+          <t>Sissel Furuholt Valle</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5.45,77</t>
+          <t>5.44,38</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>18.01.2015</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -4454,16 +4769,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Karoline Volden</t>
+          <t>Maud Steinsdotter Nestgaard</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5.46,36</t>
+          <t>5.45,77</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4489,20 +4804,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Solveig Natvig Løvseth</t>
+          <t>Karoline Volden</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5.48,84</t>
+          <t>5.46,36</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19.01.2014</t>
+          <t>18.01.2015</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4524,20 +4839,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Julie Hegvik</t>
+          <t>Solveig Natvig Løvseth</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5.49,61</t>
+          <t>5.48,84</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>24.05.2008</t>
+          <t>19.01.2014</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4559,12 +4874,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ada Fludal Osland</t>
+          <t>Julie Hegvik</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5.44,96</t>
+          <t>5.49,61</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4572,7 +4887,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>08.11.2025</t>
+          <t>24.05.2008</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4594,20 +4909,20 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Malin Schanke Tømmervik</t>
+          <t>Ada Fludal Osland</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5.49,70</t>
+          <t>5.44,96</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>24.05.2008</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4629,20 +4944,20 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sissel Furuholt Valle</t>
+          <t>Malin Schanke Tømmervik</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5.46,07</t>
+          <t>5.49,70</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>08.11.2025</t>
+          <t>24.05.2008</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4839,20 +5154,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hege Solberg Jørgensen</t>
+          <t>Emmelin Munkhaugen</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5.57,97</t>
+          <t>5.52,64</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>20.05.2017</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4874,25 +5189,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Elise Nygård</t>
+          <t>Hege Solberg Jørgensen</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5.58,41</t>
+          <t>5.57,97</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>11.03.2011</t>
+          <t>20.05.2017</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4909,25 +5224,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Elisabeth Wilmann</t>
+          <t>Elise Nygård</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6.00,40</t>
+          <t>5.58,41</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>01.10.2017</t>
+          <t>11.03.2011</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Husebybadet</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4944,25 +5259,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Kristina Elena Bjørklund Mora</t>
+          <t>Elisabeth Wilmann</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6.01,05</t>
+          <t>6.00,40</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>11.03.2011</t>
+          <t>01.10.2017</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Molde</t>
+          <t>Husebybadet</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4979,25 +5294,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Carina Aadahl</t>
+          <t>Kristina Elena Bjørklund Mora</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6.02,31</t>
+          <t>6.01,05</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19.01.2014</t>
+          <t>11.03.2011</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Molde</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5014,20 +5329,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nina Alicja Skarø</t>
+          <t>Carina Aadahl</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6.03,22</t>
+          <t>6.02,31</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>20.05.2017</t>
+          <t>19.01.2014</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -5049,20 +5364,20 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Marie Skuseth</t>
+          <t>Nina Alicja Skarø</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>6.02,55</t>
+          <t>6.03,22</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>08.11.2025</t>
+          <t>20.05.2017</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5084,12 +5399,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Eirill Straum</t>
+          <t>Marie Skuseth</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6.07,51</t>
+          <t>6.02,55</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -5097,12 +5412,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>23.10.2016</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5119,25 +5434,25 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kine Marie Sørensen</t>
+          <t>Eirill Straum</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>6.08,20</t>
+          <t>6.07,51</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>20.05.2006</t>
+          <t>23.10.2016</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5154,25 +5469,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mila Maria Flåan</t>
+          <t>Kine Marie Sørensen</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>6.09,05</t>
+          <t>6.08,20</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>23.10.2022</t>
+          <t>20.05.2006</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5189,20 +5504,20 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Thea Lervold Høffler</t>
+          <t>Mila Maria Flåan</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>6.12,19</t>
+          <t>6.09,05</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>26.10.2013</t>
+          <t>23.10.2022</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5224,25 +5539,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Frida Pauline Busch</t>
+          <t>Thea Lervold Høffler</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6.20,35</t>
+          <t>6.12,19</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>13.11.2021</t>
+          <t>26.10.2013</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5259,20 +5574,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Embla Mimi Baarholm</t>
+          <t>Anita Klungervik</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6.24,70</t>
+          <t>6.16,10</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20.05.2017</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5294,20 +5609,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Thora Bjarnøe Brandsegg</t>
+          <t>Elina Arefjord Spangelo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6.26,32</t>
+          <t>6.17,57</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>20.06.2021</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5329,20 +5644,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Nicole Kulagina</t>
+          <t>Frida Pauline Busch</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6.23,44</t>
+          <t>6.20,35</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>08.11.2025</t>
+          <t>13.11.2021</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5364,20 +5679,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hedda Østgaard</t>
+          <t>Michaela Josefin Abeleva Barrera</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6.30,23</t>
+          <t>6.20,39</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>21.06.2008</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5399,20 +5714,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Emma Lu Tjeldvoll</t>
+          <t>Embla Mimi Baarholm</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6.45,64</t>
+          <t>6.24,70</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>260</v>
+        <v>304</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>13.11.2021</t>
+          <t>20.05.2017</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5434,20 +5749,20 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Hedda Grimstad-Johannessen</t>
+          <t>Thora Bjarnøe Brandsegg</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6.46,17</t>
+          <t>6.26,32</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>259</v>
+        <v>301</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>22.06.2019</t>
+          <t>20.06.2021</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5469,20 +5784,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Emilie Ying Ulstad Hovland</t>
+          <t>Nicole Kulagina</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6.49,67</t>
+          <t>6.23,44</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>28.03.2025</t>
+          <t>08.11.2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5504,25 +5819,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Silje Dahle</t>
+          <t>Louise Thys</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6.50,04</t>
+          <t>6.29,67</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>251</v>
+        <v>293</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>22.10.2017</t>
+          <t>13.06.2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5539,20 +5854,20 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Hedda Østgaard</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7.08,22</t>
+          <t>6.30,23</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>221</v>
+        <v>292</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>15.09.2013</t>
+          <t>21.06.2008</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5574,25 +5889,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Chloe Branlat</t>
+          <t>Emma Lu Tjeldvoll</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>7.13,68</t>
+          <t>6.45,64</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>212</v>
+        <v>260</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>15.02.2025</t>
+          <t>13.11.2021</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Kolvereid</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5609,33 +5924,313 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Hedda Grimstad-Johannessen</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>6.46,17</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>259</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>22.06.2019</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Emilie Ying Ulstad Hovland</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>6.49,67</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>252</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>28.03.2025</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Silje Dahle</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>6.50,04</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>251</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>22.10.2017</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Kristiansund</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Othelie Annette Høie</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>7.08,22</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>221</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>15.09.2013</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Live Hamnes Ulriksen</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>7.09,33</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>219</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Chloe Branlat</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>7.13,68</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>212</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>15.02.2025</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Kolvereid</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Marie Wærnes Blom</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>7.26,77</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>194</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>25.01.2026</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
           <t>Ida Fiskaa Barstad</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>7.47,57</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C59" t="n">
         <v>169</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>22.06.2019</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Trondheim</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>25m</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Aurora Aarflot Johannessen</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>8.12,14</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>145</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>13.06.2026</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Trondheim</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>25m</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -5652,7 +6247,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6185,12 +6780,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Silje Aadahl</t>
+          <t>Nora Yian Baldersheim</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6.04,75</t>
+          <t>6.04,64</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -6198,12 +6793,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>09.07.2017</t>
+          <t>30.04.2022</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -6220,12 +6815,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Nora Yian Baldersheim</t>
+          <t>Silje Aadahl</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6.04,64</t>
+          <t>6.04,75</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -6233,12 +6828,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30.04.2022</t>
+          <t>09.07.2017</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -6395,25 +6990,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marthe Kalvik</t>
+          <t>Emre Vold Kirkvold</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6.13,27</t>
+          <t>5.35,87</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29.04.2006</t>
+          <t>07.06.2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6430,25 +7025,25 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Eirill Straum</t>
+          <t>Marthe Kalvik</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6.16,86</t>
+          <t>6.13,27</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>03.07.2016</t>
+          <t>29.04.2006</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -6465,25 +7060,25 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Emre Vold Kirkvold</t>
+          <t>Eirill Straum</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5.43,82</t>
+          <t>6.16,86</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>14.06.2025</t>
+          <t>03.07.2016</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -6675,25 +7270,25 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Elise Nygård</t>
+          <t>Elina Arefjord Spangelo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>6.35,80</t>
+          <t>6.34,57</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>11.06.2010</t>
+          <t>26.04.2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6710,25 +7305,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Diana Stafsnes Califano</t>
+          <t>Elise Nygård</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6.36,46</t>
+          <t>6.35,80</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>30.06.2019</t>
+          <t>11.06.2010</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Hamar</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6745,25 +7340,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Othelie Annette Høie</t>
+          <t>Diana Stafsnes Califano</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>6.36,93</t>
+          <t>6.36,46</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>30.08.2015</t>
+          <t>30.06.2019</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6780,25 +7375,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Isabella Johanne Debik</t>
+          <t>Othelie Annette Høie</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6.37,18</t>
+          <t>6.36,93</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>30.04.2022</t>
+          <t>30.08.2015</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6815,20 +7410,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Live Killingberg Sandberg</t>
+          <t>Isabella Johanne Debik</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6.45,36</t>
+          <t>6.37,18</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>15.06.2019</t>
+          <t>30.04.2022</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6850,20 +7445,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Hedda Østgaard</t>
+          <t>Alisa Kulagina</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6.54,19</t>
+          <t>6.40,72</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>26.04.2008</t>
+          <t>26.04.2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6885,33 +7480,278 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>Live Killingberg Sandberg</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>6.45,36</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>282</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>15.06.2019</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Hamar</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Louise Thys</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>6.50,97</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>270</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Hedda Østgaard</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>6.54,19</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>264</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>26.04.2008</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Ina Birgitte Eidsmo Hova</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>7.20,78</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C39" t="n">
         <v>219</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>14.06.2025</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Hamar</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>50m</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Nicoline Vinje</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>7.25,99</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>211</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>07.06.2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Live Hamnes Ulriksen</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>7.34,61</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>200</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Ilaria Kari Cherubini</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>7.50,85</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>180</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>26.04.2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Namsos</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Aurora Aarflot Johannessen</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>8.24,33</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>146</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>07.06.2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>50m</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
